--- a/output/pdf_financials_xlsx/STE.xlsx
+++ b/output/pdf_financials_xlsx/STE.xlsx
@@ -431,6 +431,26 @@
   </sheetPr>
   <dimension ref="A1:R135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/STE.xlsx
+++ b/output/pdf_financials_xlsx/STE.xlsx
@@ -6028,49 +6028,49 @@
         <v>0.947364</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.947364</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.356996</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.389882</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.389882</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.389882</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.389882</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.389882</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.389882</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.693882</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.975029</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.276092</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.042092</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.042092</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.475592</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.475592</v>
       </c>
     </row>
     <row r="93">
@@ -9564,7 +9564,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -10554,7 +10558,11 @@
           <t>Reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11247,7 +11255,11 @@
           <t>Reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -12055,7 +12067,11 @@
           <t>Reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12558,7 +12574,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -17150,7 +17170,11 @@
           <t>Share-based payment reserve (note 11)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -18063,7 +18087,11 @@
           <t>Share-based payment reserve (note 11)</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -20204,7 +20232,11 @@
           <t>Share-based payment reserve 11 1,356,996</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/STE.xlsx
+++ b/output/pdf_financials_xlsx/STE.xlsx
@@ -941,10 +941,10 @@
         <v>0.331542</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.14816</v>
+        <v>0.332932</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.146438</v>
+        <v>0.274289</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         <v>-0.331542</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.14816</v>
+        <v>-0.332932</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.146438</v>
+        <v>-0.274289</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000298</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.176777</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.0659</v>
+        <v>0.06619800000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.938848</v>
+        <v>1.115625</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.141396</v>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.0659</v>
+        <v>0.06619800000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.938848</v>
+        <v>1.115625</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.141396</v>
@@ -2458,55 +2458,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.016885</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.123139</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.123139</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000406</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000639</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000276</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002871</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000949</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.01746</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000835</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000253</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.428786</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.297784</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.336469</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.103713</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.030198</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.592546</v>
       </c>
     </row>
     <row r="35">
@@ -2574,55 +2574,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.349626</v>
+        <v>0.366511</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.800518</v>
+        <v>0.923657</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.800518</v>
+        <v>0.923657</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.925272</v>
+        <v>0.925678</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.771406</v>
+        <v>0.772045</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.415853</v>
+        <v>0.416129</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002871</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000949</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.01746</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000835</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.000253</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.428786</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>5.297784</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.336469</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.103713</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.030198</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.592546</v>
       </c>
     </row>
     <row r="37">
@@ -3288,37 +3288,37 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.010227</v>
+        <v>0.007356</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.417129</v>
+        <v>0.41618</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.134981</v>
+        <v>0.117521</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.031967</v>
+        <v>0.031132</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.011298</v>
+        <v>0.011045</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.476653</v>
+        <v>0.047867</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>6.527267</v>
+        <v>1.229483</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.421297</v>
+        <v>0.084828</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.242486</v>
+        <v>0.138773</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.134625</v>
+        <v>0.104427</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.685965</v>
+        <v>0.093419</v>
       </c>
     </row>
     <row r="49">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
@@ -16261,7 +16261,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -18800,7 +18804,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -19204,7 +19208,11 @@
           <t>Reclamation deposits 7 10,000</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -21040,7 +21048,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>0.025</v>
       </c>
@@ -29010,7 +29022,11 @@
           <t>Return of reclamation deposit</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -30343,7 +30359,11 @@
           <t>Return of reclamation deposit 10,000</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -46630,7 +46650,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -56787,7 +56807,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -62924,7 +62944,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E543" s="5" t="n">
